--- a/output/pdf_financials_xlsx/VLI.xlsx
+++ b/output/pdf_financials_xlsx/VLI.xlsx
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>54.082114</v>
+        <v>55.37669</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>81.00098300000001</v>
+        <v>80.575329</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2677,28 +2677,28 @@
         <v>0.770282</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.340964</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.246245</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.515352</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.159036</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.041908</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.990128</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.907945</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.32917</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.453474</v>
@@ -2710,13 +2710,13 @@
         <v>0.744605</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0.09070499999999999</v>
+        <v>0.078057</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.078057</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.030549</v>
       </c>
     </row>
     <row r="35">
@@ -2787,28 +2787,28 @@
         <v>0.770282</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.340964</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.246245</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.515352</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.159036</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.041908</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.990128</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.907945</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.32917</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.453474</v>
@@ -2820,13 +2820,13 @@
         <v>0.744605</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.09070499999999999</v>
+        <v>0.078057</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.078057</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.030549</v>
       </c>
     </row>
     <row r="37">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -52130,7 +52130,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E470" s="5" t="n">

--- a/output/pdf_financials_xlsx/VLI.xlsx
+++ b/output/pdf_financials_xlsx/VLI.xlsx
@@ -782,31 +782,31 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.7039339999999999</v>
+        <v>0.782437</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.607936</v>
+        <v>0.65272</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.081167</v>
+        <v>0.105848</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.013724</v>
+        <v>0.040384</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.011097</v>
+        <v>0.034997</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.001353</v>
+        <v>0.02181</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.001641</v>
+        <v>0.020966</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.187427</v>
+        <v>0.20185</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.456676</v>
+        <v>0.472509</v>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
@@ -995,13 +995,13 @@
         <v>1.466928</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.081167</v>
+        <v>0.105848</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.013724</v>
+        <v>0.040384</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.011097</v>
+        <v>0.034997</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.189688</v>
@@ -4777,22 +4777,22 @@
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.02634</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.036057</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.031252</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.027525</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.027525</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="71">
@@ -4832,22 +4832,22 @@
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.02634</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.036057</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.031252</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.027525</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.027525</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="72">
@@ -5052,22 +5052,22 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.2065</v>
+        <v>0.18016</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.158614</v>
+        <v>0.122557</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.031252</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.027525</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.027525</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.124425</v>
+        <v>0.107825</v>
       </c>
     </row>
     <row r="76">
@@ -5356,35 +5356,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L80" s="3" t="n">
+        <v>0.001983465548054347</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.001916184963265017</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.001579189863270617</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.001658915518258166</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.001658915518258166</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.001234032658153923</v>
       </c>
     </row>
     <row r="81">
@@ -9828,7 +9816,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -13060,7 +13052,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -15962,7 +15958,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -37712,7 +37712,11 @@
           <t>Issuance of shares by private placement</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -39336,7 +39340,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -40390,7 +40398,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E345" s="5" t="n">
         <v>-1.292012</v>
       </c>
@@ -43208,7 +43220,11 @@
           <t>Stationery and office expenses</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -50410,7 +50426,11 @@
           <t>Stationery and office expenses</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E452" s="5" t="n">
         <v>0.078503</v>
       </c>
@@ -51740,7 +51760,11 @@
           <t>Interest revenues</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E466" s="5" t="n">
         <v>-0.005048</v>
       </c>
